--- a/Test_data/New_Architecture/Complex_Scenario/Marks.xlsx
+++ b/Test_data/New_Architecture/Complex_Scenario/Marks.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\madha\Desktop\attainment_software\Test_data\New_Architecture\Complex_Scenario\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7C557AD1-03F0-498E-B658-E514C858E171}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F3BFF540-B124-450C-832F-5A8650FFD7B7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-22845" yWindow="4980" windowWidth="18900" windowHeight="10890" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-25320" yWindow="2505" windowWidth="25440" windowHeight="15270" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="CCE1" sheetId="1" r:id="rId1"/>
@@ -1216,7 +1216,7 @@
         <v>3</v>
       </c>
       <c r="B2">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="C2">
         <v>3.7</v>
@@ -1227,7 +1227,7 @@
         <v>4</v>
       </c>
       <c r="B3">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="C3">
         <v>3.5</v>
@@ -1238,7 +1238,7 @@
         <v>5</v>
       </c>
       <c r="B4">
-        <v>4.4000000000000004</v>
+        <v>0</v>
       </c>
       <c r="C4">
         <v>4.5999999999999996</v>
@@ -1249,7 +1249,7 @@
         <v>6</v>
       </c>
       <c r="B5">
-        <v>4.4000000000000004</v>
+        <v>0</v>
       </c>
       <c r="C5">
         <v>3.7</v>
@@ -1260,7 +1260,7 @@
         <v>7</v>
       </c>
       <c r="B6">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="C6">
         <v>3.7</v>
@@ -1271,7 +1271,7 @@
         <v>8</v>
       </c>
       <c r="B7">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="C7">
         <v>4</v>
@@ -1282,7 +1282,7 @@
         <v>9</v>
       </c>
       <c r="B8">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="C8">
         <v>3.5</v>
@@ -1293,10 +1293,10 @@
         <v>10</v>
       </c>
       <c r="B9">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="C9">
-        <v>4.5999999999999996</v>
+        <v>3</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.3">
@@ -1304,10 +1304,10 @@
         <v>11</v>
       </c>
       <c r="B10">
-        <v>4.0999999999999996</v>
+        <v>0</v>
       </c>
       <c r="C10">
-        <v>3.8</v>
+        <v>3</v>
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.3">
@@ -1315,10 +1315,10 @@
         <v>12</v>
       </c>
       <c r="B11">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="C11">
-        <v>4.5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.3">
@@ -1326,10 +1326,10 @@
         <v>13</v>
       </c>
       <c r="B12">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="C12">
-        <v>4.4000000000000004</v>
+        <v>3</v>
       </c>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.3">
@@ -1337,10 +1337,10 @@
         <v>14</v>
       </c>
       <c r="B13">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="C13">
-        <v>3.6</v>
+        <v>3</v>
       </c>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.3">
@@ -1348,10 +1348,10 @@
         <v>15</v>
       </c>
       <c r="B14">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="C14">
-        <v>4.5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.3">
@@ -1359,10 +1359,10 @@
         <v>16</v>
       </c>
       <c r="B15">
-        <v>4.4000000000000004</v>
+        <v>0</v>
       </c>
       <c r="C15">
-        <v>3.4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.3">
@@ -1370,10 +1370,10 @@
         <v>17</v>
       </c>
       <c r="B16">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="C16">
-        <v>4.3</v>
+        <v>3</v>
       </c>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.3">
@@ -1381,10 +1381,10 @@
         <v>18</v>
       </c>
       <c r="B17">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="C17">
-        <v>4.2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.3">
@@ -1392,10 +1392,10 @@
         <v>19</v>
       </c>
       <c r="B18">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="C18">
-        <v>3.6</v>
+        <v>3</v>
       </c>
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.3">
@@ -1403,10 +1403,10 @@
         <v>20</v>
       </c>
       <c r="B19">
-        <v>4.5999999999999996</v>
+        <v>0</v>
       </c>
       <c r="C19">
-        <v>4.5999999999999996</v>
+        <v>3</v>
       </c>
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.3">
@@ -1414,10 +1414,10 @@
         <v>21</v>
       </c>
       <c r="B20">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="C20">
-        <v>3.4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.3">
@@ -1425,7 +1425,7 @@
         <v>22</v>
       </c>
       <c r="B21">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="C21">
         <v>4</v>
@@ -2822,7 +2822,7 @@
         <v>7.8</v>
       </c>
       <c r="D10">
-        <v>9.1999999999999993</v>
+        <v>5</v>
       </c>
       <c r="E10">
         <v>7.5</v>
@@ -2845,7 +2845,7 @@
         <v>6.7</v>
       </c>
       <c r="D11">
-        <v>7.4</v>
+        <v>5</v>
       </c>
       <c r="E11">
         <v>6.6</v>
@@ -2868,7 +2868,7 @@
         <v>8</v>
       </c>
       <c r="D12">
-        <v>8.1999999999999993</v>
+        <v>5</v>
       </c>
       <c r="E12">
         <v>7</v>
@@ -2891,7 +2891,7 @@
         <v>9.4</v>
       </c>
       <c r="D13">
-        <v>8.1</v>
+        <v>5</v>
       </c>
       <c r="E13">
         <v>7</v>
@@ -2914,7 +2914,7 @@
         <v>9.1</v>
       </c>
       <c r="D14">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="E14">
         <v>6.7</v>
@@ -2937,7 +2937,7 @@
         <v>6.8</v>
       </c>
       <c r="D15">
-        <v>8.8000000000000007</v>
+        <v>5</v>
       </c>
       <c r="E15">
         <v>7.4</v>
@@ -2960,7 +2960,7 @@
         <v>9.3000000000000007</v>
       </c>
       <c r="D16">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="E16">
         <v>7.5</v>
@@ -2983,7 +2983,7 @@
         <v>7.8</v>
       </c>
       <c r="D17">
-        <v>7.3</v>
+        <v>5</v>
       </c>
       <c r="E17">
         <v>8.6</v>
@@ -3006,7 +3006,7 @@
         <v>7.9</v>
       </c>
       <c r="D18">
-        <v>7.6</v>
+        <v>5</v>
       </c>
       <c r="E18">
         <v>8.9</v>
@@ -3029,7 +3029,7 @@
         <v>7.3</v>
       </c>
       <c r="D19">
-        <v>7.5</v>
+        <v>5</v>
       </c>
       <c r="E19">
         <v>7.5</v>
@@ -3052,7 +3052,7 @@
         <v>9</v>
       </c>
       <c r="D20">
-        <v>7.3</v>
+        <v>5</v>
       </c>
       <c r="E20">
         <v>9.1999999999999993</v>
@@ -3167,7 +3167,7 @@
         <v>8.4</v>
       </c>
       <c r="D25">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="E25">
         <v>9.3000000000000007</v>
@@ -3190,7 +3190,7 @@
         <v>7.7</v>
       </c>
       <c r="D26">
-        <v>6.5</v>
+        <v>2</v>
       </c>
       <c r="E26">
         <v>6.5</v>
@@ -3213,7 +3213,7 @@
         <v>6.7</v>
       </c>
       <c r="D27">
-        <v>7.1</v>
+        <v>2</v>
       </c>
       <c r="E27">
         <v>6.5</v>
@@ -3236,7 +3236,7 @@
         <v>7.9</v>
       </c>
       <c r="D28">
-        <v>9.1999999999999993</v>
+        <v>2</v>
       </c>
       <c r="E28">
         <v>7.5</v>
@@ -3259,7 +3259,7 @@
         <v>8</v>
       </c>
       <c r="D29">
-        <v>7.1</v>
+        <v>2</v>
       </c>
       <c r="E29">
         <v>7.3</v>
@@ -3282,7 +3282,7 @@
         <v>6.8</v>
       </c>
       <c r="D30">
-        <v>8.4</v>
+        <v>2</v>
       </c>
       <c r="E30">
         <v>7.3</v>
@@ -3305,7 +3305,7 @@
         <v>7.5</v>
       </c>
       <c r="D31">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="E31">
         <v>6.6</v>
@@ -3361,7 +3361,7 @@
         <v>2.2999999999999998</v>
       </c>
       <c r="D2">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="E2">
         <v>2</v>
@@ -3384,7 +3384,7 @@
         <v>2.8</v>
       </c>
       <c r="D3">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E3">
         <v>2.4</v>
@@ -3407,7 +3407,7 @@
         <v>2.7</v>
       </c>
       <c r="D4">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="E4">
         <v>2.7</v>
@@ -3430,7 +3430,7 @@
         <v>2.2999999999999998</v>
       </c>
       <c r="D5">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="E5">
         <v>2.7</v>
@@ -3453,7 +3453,7 @@
         <v>2.8</v>
       </c>
       <c r="D6">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="E6">
         <v>2.4</v>
@@ -3476,7 +3476,7 @@
         <v>2.8</v>
       </c>
       <c r="D7">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="E7">
         <v>2</v>
@@ -3499,7 +3499,7 @@
         <v>2.5</v>
       </c>
       <c r="D8">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="E8">
         <v>2</v>
@@ -3522,7 +3522,7 @@
         <v>2.6</v>
       </c>
       <c r="D9">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="E9">
         <v>2.1</v>
@@ -3545,7 +3545,7 @@
         <v>2.7</v>
       </c>
       <c r="D10">
-        <v>2.2000000000000002</v>
+        <v>1.2</v>
       </c>
       <c r="E10">
         <v>2.8</v>
@@ -3568,7 +3568,7 @@
         <v>2.8</v>
       </c>
       <c r="D11">
-        <v>2.8</v>
+        <v>1.2</v>
       </c>
       <c r="E11">
         <v>2.2999999999999998</v>
@@ -3591,7 +3591,7 @@
         <v>2.7</v>
       </c>
       <c r="D12">
-        <v>2.7</v>
+        <v>1.2</v>
       </c>
       <c r="E12">
         <v>2.8</v>
@@ -3614,7 +3614,7 @@
         <v>2.7</v>
       </c>
       <c r="D13">
-        <v>2.7</v>
+        <v>1.2</v>
       </c>
       <c r="E13">
         <v>2.2999999999999998</v>
@@ -3637,7 +3637,7 @@
         <v>2.6</v>
       </c>
       <c r="D14">
-        <v>2.1</v>
+        <v>1.2</v>
       </c>
       <c r="E14">
         <v>2.5</v>
@@ -3660,7 +3660,7 @@
         <v>2.6</v>
       </c>
       <c r="D15">
-        <v>2</v>
+        <v>1.2</v>
       </c>
       <c r="E15">
         <v>2.2000000000000002</v>
@@ -3683,7 +3683,7 @@
         <v>2.4</v>
       </c>
       <c r="D16">
-        <v>2.7</v>
+        <v>1.2</v>
       </c>
       <c r="E16">
         <v>2.1</v>
@@ -3706,7 +3706,7 @@
         <v>2.4</v>
       </c>
       <c r="D17">
-        <v>2.2999999999999998</v>
+        <v>1.2</v>
       </c>
       <c r="E17">
         <v>2</v>
@@ -3729,7 +3729,7 @@
         <v>2.7</v>
       </c>
       <c r="D18">
-        <v>2.5</v>
+        <v>1.2</v>
       </c>
       <c r="E18">
         <v>2.1</v>
@@ -3752,7 +3752,7 @@
         <v>2.8</v>
       </c>
       <c r="D19">
-        <v>2.2999999999999998</v>
+        <v>1.2</v>
       </c>
       <c r="E19">
         <v>2.6</v>
@@ -3775,7 +3775,7 @@
         <v>2.2999999999999998</v>
       </c>
       <c r="D20">
-        <v>2</v>
+        <v>1.2</v>
       </c>
       <c r="E20">
         <v>2.1</v>
